--- a/spec/2026겨울주니어.xlsx
+++ b/spec/2026겨울주니어.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\중국풀패턴\본공장풀패턴\2026\2026겨울풀패턴\2026겨울사이즈스펙\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\중국풀패턴\작지싸이즈스펙\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E263C90A-348B-49C4-BB03-4C8C3DF90F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C81A16-405C-46B1-9F2D-C53AC8004240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="776" xr2:uid="{3359282B-7569-4BC7-A037-9A98D8DF6EA5}"/>
   </bookViews>
@@ -29,8 +29,9 @@
     <sheet name="TO02" sheetId="1038" r:id="rId14"/>
     <sheet name="TO03" sheetId="1042" r:id="rId15"/>
     <sheet name="TO04" sheetId="1040" r:id="rId16"/>
-    <sheet name="TO06" sheetId="1043" r:id="rId17"/>
-    <sheet name="TO07" sheetId="1044" r:id="rId18"/>
+    <sheet name="TO05" sheetId="1048" r:id="rId17"/>
+    <sheet name="TO06" sheetId="1043" r:id="rId18"/>
+    <sheet name="TO07" sheetId="1044" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'OU01'!$A$1:$M$40</definedName>
@@ -49,15 +50,16 @@
     <definedName name="_xlnm.Print_Area" localSheetId="13">'TO02'!$A$1:$M$38</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">'TO03'!$A$1:$M$36</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'TO04'!$A$1:$M$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="16">'TO06'!$A$1:$M$40</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="17">'TO07'!$A$1:$M$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'TO05'!$A$1:$M$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="17">'TO06'!$A$1:$M$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="18">'TO07'!$A$1:$M$36</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1294" uniqueCount="311">
   <si>
     <t xml:space="preserve">STRIGHT </t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -797,6 +799,18 @@
   </si>
   <si>
     <t>앞중심</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>COLLARD WIDTH</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>카라 폭</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>중심</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
@@ -1493,12 +1507,54 @@
     <t>오비포함 앞절개선 와끼기준</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">소매 밑단(시보리 밑단)의 둘레 길이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(접밴드 완성사이즈)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STYLE NO: GYFTO05-W#R21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>앞중심에서 수평으로</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">STRIGHT (1/2) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(접밴드 완성사이즈)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1616,6 +1672,14 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="7.5"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1637,7 +1701,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="58">
+  <borders count="61">
     <border>
       <left/>
       <right/>
@@ -2191,6 +2255,39 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thick">
         <color auto="1"/>
       </left>
@@ -2348,7 +2445,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2367,13 +2464,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2586,7 +2683,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2610,7 +2707,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2724,40 +2821,67 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3081,7 +3205,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -3495,7 +3619,7 @@
       </c>
       <c r="C18" s="37"/>
       <c r="D18" s="38" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E18" s="39"/>
       <c r="F18" s="39"/>
@@ -3842,7 +3966,7 @@
         <v>16</v>
       </c>
       <c r="B33" s="52" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C33" s="52"/>
       <c r="D33" s="45"/>
@@ -3867,7 +3991,7 @@
     <row r="34" spans="1:13" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="22"/>
       <c r="B34" s="37" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="38"/>
@@ -3894,15 +4018,15 @@
       <c r="F35" s="63"/>
       <c r="G35" s="64"/>
       <c r="H35" s="29">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="I35" s="31">
-        <f>SUM(H35)+0.2</f>
-        <v>5.7</v>
+        <f>SUM(H35)+0.4</f>
+        <v>7.4</v>
       </c>
       <c r="J35" s="31">
-        <f>SUM(I35)+0.2</f>
-        <v>5.9</v>
+        <f>SUM(I35)+0.4</f>
+        <v>7.8000000000000007</v>
       </c>
       <c r="K35" s="32"/>
       <c r="L35" s="32"/>
@@ -3915,7 +4039,7 @@
       </c>
       <c r="C36" s="51"/>
       <c r="D36" s="38" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E36" s="39"/>
       <c r="F36" s="39"/>
@@ -4427,7 +4551,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -4678,7 +4802,7 @@
       </c>
       <c r="C13" s="44"/>
       <c r="D13" s="45" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E13" s="46"/>
       <c r="F13" s="46"/>
@@ -4751,7 +4875,7 @@
       </c>
       <c r="C16" s="98"/>
       <c r="D16" s="88" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E16" s="108"/>
       <c r="F16" s="108"/>
@@ -4885,7 +5009,7 @@
       </c>
       <c r="C22" s="98"/>
       <c r="D22" s="38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E22" s="39"/>
       <c r="F22" s="39"/>
@@ -4926,7 +5050,7 @@
       <c r="L23" s="52"/>
       <c r="M23" s="106"/>
       <c r="P23" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" spans="1:16" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5128,7 +5252,7 @@
       </c>
       <c r="C32" s="98"/>
       <c r="D32" s="88" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E32" s="84"/>
       <c r="F32" s="84"/>
@@ -5193,7 +5317,7 @@
         <v>17</v>
       </c>
       <c r="B35" s="43" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C35" s="44"/>
       <c r="D35" s="45"/>
@@ -5218,7 +5342,7 @@
     <row r="36" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="91"/>
       <c r="B36" s="97" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C36" s="98"/>
       <c r="D36" s="83"/>
@@ -5354,7 +5478,7 @@
       </c>
       <c r="C42" s="24"/>
       <c r="D42" s="25" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E42" s="26"/>
       <c r="F42" s="26"/>
@@ -5400,7 +5524,7 @@
       </c>
       <c r="C44" s="24"/>
       <c r="D44" s="25" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E44" s="26"/>
       <c r="F44" s="26"/>
@@ -5461,21 +5585,10 @@
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:I8"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="D4:G4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:G5"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="K7:K8"/>
     <mergeCell ref="L7:L8"/>
@@ -5485,6 +5598,12 @@
     <mergeCell ref="K5:K6"/>
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="M5:M6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D6:G6"/>
     <mergeCell ref="A11:A12"/>
@@ -5497,6 +5616,11 @@
     <mergeCell ref="D9:G9"/>
     <mergeCell ref="H9:H10"/>
     <mergeCell ref="I9:I10"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:I8"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="K11:K12"/>
     <mergeCell ref="L11:L12"/>
@@ -5721,7 +5845,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -6023,7 +6147,7 @@
     <row r="14" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="91"/>
       <c r="B14" s="97" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C14" s="98"/>
       <c r="D14" s="83" t="s">
@@ -6935,7 +7059,6 @@
     <mergeCell ref="D13:G13"/>
     <mergeCell ref="H13:H14"/>
     <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J11:J12"/>
     <mergeCell ref="K11:K12"/>
     <mergeCell ref="L11:L12"/>
     <mergeCell ref="M11:M12"/>
@@ -6947,6 +7070,12 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="D10:G10"/>
     <mergeCell ref="J9:J10"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D6:G6"/>
     <mergeCell ref="A11:A12"/>
@@ -6964,16 +7093,7 @@
     <mergeCell ref="D7:G7"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="I7:I8"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:G5"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J11:J12"/>
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="K7:K8"/>
     <mergeCell ref="L7:L8"/>
@@ -6993,6 +7113,10 @@
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:G4"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -7018,7 +7142,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -7142,7 +7266,7 @@
       </c>
       <c r="C6" s="98"/>
       <c r="D6" s="83" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E6" s="84"/>
       <c r="F6" s="84"/>
@@ -7864,7 +7988,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -8471,7 +8595,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="129" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C27" s="130"/>
       <c r="D27" s="131"/>
@@ -8496,7 +8620,7 @@
     <row r="28" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="22"/>
       <c r="B28" s="50" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C28" s="51"/>
       <c r="D28" s="38" t="s">
@@ -8517,7 +8641,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C29" s="24"/>
       <c r="D29" s="124" t="s">
@@ -8544,7 +8668,7 @@
     <row r="30" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="22"/>
       <c r="B30" s="23" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C30" s="24"/>
       <c r="D30" s="38" t="s">
@@ -8640,7 +8764,7 @@
       </c>
       <c r="C34" s="70"/>
       <c r="D34" s="71" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E34" s="72"/>
       <c r="F34" s="72"/>
@@ -8912,7 +9036,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -9222,7 +9346,7 @@
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="38" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E14" s="39"/>
       <c r="F14" s="39"/>
@@ -9270,7 +9394,7 @@
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="38" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E16" s="39"/>
       <c r="F16" s="39"/>
@@ -9318,7 +9442,7 @@
       </c>
       <c r="C18" s="37"/>
       <c r="D18" s="38" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E18" s="39"/>
       <c r="F18" s="39"/>
@@ -9686,7 +9810,7 @@
       </c>
       <c r="C34" s="24"/>
       <c r="D34" s="25" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E34" s="26"/>
       <c r="F34" s="26"/>
@@ -9703,7 +9827,7 @@
         <v>17</v>
       </c>
       <c r="B35" s="43" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C35" s="44"/>
       <c r="D35" s="53"/>
@@ -9728,11 +9852,11 @@
     <row r="36" spans="1:13" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="77"/>
       <c r="B36" s="50" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C36" s="51"/>
       <c r="D36" s="88" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E36" s="39"/>
       <c r="F36" s="39"/>
@@ -9778,7 +9902,7 @@
       </c>
       <c r="C38" s="70"/>
       <c r="D38" s="71" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E38" s="72"/>
       <c r="F38" s="72"/>
@@ -10177,7 +10301,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -10255,7 +10379,7 @@
       </c>
       <c r="C4" s="78"/>
       <c r="D4" s="25" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
@@ -10272,7 +10396,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C5" s="44"/>
       <c r="D5" s="53" t="s">
@@ -10299,11 +10423,11 @@
     <row r="6" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="55"/>
       <c r="B6" s="50" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C6" s="51"/>
       <c r="D6" s="38" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E6" s="39"/>
       <c r="F6" s="39"/>
@@ -10539,11 +10663,11 @@
     <row r="16" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="55"/>
       <c r="B16" s="37" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="38" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E16" s="39"/>
       <c r="F16" s="39"/>
@@ -10591,7 +10715,7 @@
       </c>
       <c r="C18" s="37"/>
       <c r="D18" s="38" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E18" s="39"/>
       <c r="F18" s="39"/>
@@ -10635,7 +10759,7 @@
     <row r="20" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="55"/>
       <c r="B20" s="37" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="38" t="s">
@@ -10829,7 +10953,7 @@
       </c>
       <c r="C28" s="24"/>
       <c r="D28" s="25" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E28" s="26"/>
       <c r="F28" s="26"/>
@@ -11224,7 +11348,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -11254,7 +11378,7 @@
       <c r="F2" s="20"/>
       <c r="G2" s="20"/>
       <c r="H2" s="13" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>33</v>
@@ -12359,6 +12483,1063 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2682309-D351-43CA-A287-A7373DF8FB6B}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
+  <dimension ref="A1:P60"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.75" customWidth="1"/>
+    <col min="4" max="7" width="8.125" customWidth="1"/>
+    <col min="8" max="14" width="5.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="19"/>
+    </row>
+    <row r="2" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+    </row>
+    <row r="3" spans="1:16" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="21">
+        <v>1</v>
+      </c>
+      <c r="B3" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="74"/>
+      <c r="D3" s="75" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="28">
+        <v>52</v>
+      </c>
+      <c r="I3" s="30">
+        <f>SUM(H3)+3</f>
+        <v>55</v>
+      </c>
+      <c r="J3" s="30">
+        <f>SUM(I3)+3</f>
+        <v>58</v>
+      </c>
+      <c r="K3" s="33"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="35"/>
+    </row>
+    <row r="4" spans="1:16" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="77"/>
+      <c r="B4" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="78"/>
+      <c r="D4" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="67"/>
+    </row>
+    <row r="5" spans="1:16" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="22">
+        <v>2</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="44"/>
+      <c r="D5" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="48">
+        <v>56</v>
+      </c>
+      <c r="I5" s="32">
+        <f>SUM(H5)+4.2</f>
+        <v>60.2</v>
+      </c>
+      <c r="J5" s="32">
+        <f>SUM(I5)+4.2</f>
+        <v>64.400000000000006</v>
+      </c>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="41"/>
+    </row>
+    <row r="6" spans="1:16" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="22"/>
+      <c r="B6" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="51"/>
+      <c r="D6" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="41"/>
+    </row>
+    <row r="7" spans="1:16" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="22">
+        <v>3</v>
+      </c>
+      <c r="B7" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="52"/>
+      <c r="D7" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="48">
+        <v>53</v>
+      </c>
+      <c r="I7" s="32">
+        <f>SUM(H7)+4</f>
+        <v>57</v>
+      </c>
+      <c r="J7" s="32">
+        <f>SUM(I7)+4</f>
+        <v>61</v>
+      </c>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="41"/>
+    </row>
+    <row r="8" spans="1:16" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="22"/>
+      <c r="B8" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="37"/>
+      <c r="D8" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="41"/>
+    </row>
+    <row r="9" spans="1:16" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="22">
+        <v>4</v>
+      </c>
+      <c r="B9" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="52"/>
+      <c r="D9" s="53" t="s">
+        <v>310</v>
+      </c>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="48">
+        <v>94</v>
+      </c>
+      <c r="I9" s="32">
+        <f>SUM(H9)+8</f>
+        <v>102</v>
+      </c>
+      <c r="J9" s="32">
+        <f>SUM(I9)+8</f>
+        <v>110</v>
+      </c>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="41"/>
+      <c r="P9" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="22"/>
+      <c r="B10" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="37"/>
+      <c r="D10" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="34"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="41"/>
+    </row>
+    <row r="11" spans="1:16" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="22">
+        <v>5</v>
+      </c>
+      <c r="B11" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="52"/>
+      <c r="D11" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="29">
+        <v>22</v>
+      </c>
+      <c r="I11" s="31">
+        <f>SUM(H11)+1</f>
+        <v>23</v>
+      </c>
+      <c r="J11" s="31">
+        <f>SUM(I11)+1</f>
+        <v>24</v>
+      </c>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="41"/>
+    </row>
+    <row r="12" spans="1:16" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="22"/>
+      <c r="B12" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="37"/>
+      <c r="D12" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
+      <c r="M12" s="41"/>
+    </row>
+    <row r="13" spans="1:16" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="22">
+        <v>6</v>
+      </c>
+      <c r="B13" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="52"/>
+      <c r="D13" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="29">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="I13" s="31">
+        <f>SUM(H13)+0.6</f>
+        <v>17.700000000000003</v>
+      </c>
+      <c r="J13" s="31">
+        <f>SUM(I13)+0.6</f>
+        <v>18.300000000000004</v>
+      </c>
+      <c r="K13" s="31"/>
+      <c r="L13" s="31"/>
+      <c r="M13" s="41"/>
+    </row>
+    <row r="14" spans="1:16" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="22"/>
+      <c r="B14" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="37"/>
+      <c r="D14" s="38" t="s">
+        <v>258</v>
+      </c>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="31"/>
+      <c r="M14" s="41"/>
+    </row>
+    <row r="15" spans="1:16" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="22">
+        <v>7</v>
+      </c>
+      <c r="B15" s="52" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="52"/>
+      <c r="D15" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="29">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="I15" s="31">
+        <f>SUM(H15)+0.3</f>
+        <v>8.5</v>
+      </c>
+      <c r="J15" s="31">
+        <f>SUM(I15)+0.3</f>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="K15" s="31"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="41"/>
+    </row>
+    <row r="16" spans="1:16" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="22"/>
+      <c r="B16" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="37"/>
+      <c r="D16" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
+      <c r="M16" s="41"/>
+    </row>
+    <row r="17" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="22">
+        <v>8</v>
+      </c>
+      <c r="B17" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="44"/>
+      <c r="D17" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="29">
+        <v>45.7</v>
+      </c>
+      <c r="I17" s="31">
+        <f>SUM(H17)+1.6</f>
+        <v>47.300000000000004</v>
+      </c>
+      <c r="J17" s="31">
+        <f>SUM(I17)+1.6</f>
+        <v>48.900000000000006</v>
+      </c>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="41"/>
+    </row>
+    <row r="18" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="22"/>
+      <c r="B18" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="37"/>
+      <c r="D18" s="38" t="s">
+        <v>239</v>
+      </c>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="31"/>
+      <c r="M18" s="41"/>
+    </row>
+    <row r="19" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="22">
+        <v>9</v>
+      </c>
+      <c r="B19" s="142" t="s">
+        <v>182</v>
+      </c>
+      <c r="C19" s="44"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="48">
+        <v>6</v>
+      </c>
+      <c r="I19" s="32">
+        <f>SUM(H19)+0.2</f>
+        <v>6.2</v>
+      </c>
+      <c r="J19" s="32">
+        <f t="shared" ref="J19" si="0">SUM(I19)+0.2</f>
+        <v>6.4</v>
+      </c>
+      <c r="K19" s="137"/>
+      <c r="L19" s="137"/>
+      <c r="M19" s="139"/>
+    </row>
+    <row r="20" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="22"/>
+      <c r="B20" s="141" t="s">
+        <v>183</v>
+      </c>
+      <c r="C20" s="51"/>
+      <c r="D20" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="34"/>
+      <c r="K20" s="138"/>
+      <c r="L20" s="138"/>
+      <c r="M20" s="140"/>
+    </row>
+    <row r="21" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="22">
+        <v>10</v>
+      </c>
+      <c r="B21" s="52" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="52"/>
+      <c r="D21" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="29">
+        <v>43</v>
+      </c>
+      <c r="I21" s="31">
+        <f>SUM(H21)+1.9</f>
+        <v>44.9</v>
+      </c>
+      <c r="J21" s="31">
+        <f>SUM(I21)+1.9</f>
+        <v>46.8</v>
+      </c>
+      <c r="K21" s="31"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="41"/>
+    </row>
+    <row r="22" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="22"/>
+      <c r="B22" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="37"/>
+      <c r="D22" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="41"/>
+    </row>
+    <row r="23" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="22">
+        <v>11</v>
+      </c>
+      <c r="B23" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="52"/>
+      <c r="D23" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="29">
+        <v>44</v>
+      </c>
+      <c r="I23" s="31">
+        <f>SUM(H23)+2</f>
+        <v>46</v>
+      </c>
+      <c r="J23" s="31">
+        <f>SUM(I23)+2</f>
+        <v>48</v>
+      </c>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="41"/>
+    </row>
+    <row r="24" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="22"/>
+      <c r="B24" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="37"/>
+      <c r="D24" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="41"/>
+    </row>
+    <row r="25" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="22">
+        <v>12</v>
+      </c>
+      <c r="B25" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="44"/>
+      <c r="D25" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="29">
+        <v>22</v>
+      </c>
+      <c r="I25" s="31">
+        <f>SUM(H25)+1</f>
+        <v>23</v>
+      </c>
+      <c r="J25" s="31">
+        <f>SUM(I25)+1</f>
+        <v>24</v>
+      </c>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="41"/>
+    </row>
+    <row r="26" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="22"/>
+      <c r="B26" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="37"/>
+      <c r="D26" s="38" t="s">
+        <v>307</v>
+      </c>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="41"/>
+    </row>
+    <row r="27" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="22">
+        <v>13</v>
+      </c>
+      <c r="B27" s="43" t="s">
+        <v>201</v>
+      </c>
+      <c r="C27" s="44"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="64"/>
+      <c r="H27" s="29">
+        <v>14.5</v>
+      </c>
+      <c r="I27" s="31">
+        <f>SUM(H27)+0.6</f>
+        <v>15.1</v>
+      </c>
+      <c r="J27" s="31">
+        <f>SUM(I27)+0.6</f>
+        <v>15.7</v>
+      </c>
+      <c r="K27" s="32"/>
+      <c r="L27" s="32"/>
+      <c r="M27" s="143"/>
+    </row>
+    <row r="28" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="22"/>
+      <c r="B28" s="97" t="s">
+        <v>202</v>
+      </c>
+      <c r="C28" s="98"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="144"/>
+    </row>
+    <row r="29" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="22">
+        <v>14</v>
+      </c>
+      <c r="B29" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="C29" s="44"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="29">
+        <v>19</v>
+      </c>
+      <c r="I29" s="31">
+        <f>SUM(H29)+0.5</f>
+        <v>19.5</v>
+      </c>
+      <c r="J29" s="31">
+        <f>SUM(I29)+0.5</f>
+        <v>20</v>
+      </c>
+      <c r="K29" s="32"/>
+      <c r="L29" s="32"/>
+      <c r="M29" s="143"/>
+    </row>
+    <row r="30" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="22"/>
+      <c r="B30" s="37" t="s">
+        <v>286</v>
+      </c>
+      <c r="C30" s="37"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="42"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="31"/>
+      <c r="J30" s="31"/>
+      <c r="K30" s="34"/>
+      <c r="L30" s="34"/>
+      <c r="M30" s="144"/>
+    </row>
+    <row r="31" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="22">
+        <v>15</v>
+      </c>
+      <c r="B31" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31" s="44"/>
+      <c r="D31" s="62"/>
+      <c r="E31" s="63"/>
+      <c r="F31" s="63"/>
+      <c r="G31" s="64"/>
+      <c r="H31" s="49">
+        <v>13.5</v>
+      </c>
+      <c r="I31" s="31">
+        <f>SUM(H31)+0.6</f>
+        <v>14.1</v>
+      </c>
+      <c r="J31" s="31">
+        <f>SUM(I31)+0.6</f>
+        <v>14.7</v>
+      </c>
+      <c r="K31" s="34"/>
+      <c r="L31" s="34"/>
+      <c r="M31" s="144"/>
+    </row>
+    <row r="32" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="22"/>
+      <c r="B32" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="C32" s="24"/>
+      <c r="D32" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="48"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="86"/>
+    </row>
+    <row r="33" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="22">
+        <v>16</v>
+      </c>
+      <c r="B33" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="C33" s="44"/>
+      <c r="D33" s="62"/>
+      <c r="E33" s="63"/>
+      <c r="F33" s="63"/>
+      <c r="G33" s="64"/>
+      <c r="H33" s="29">
+        <v>6.5</v>
+      </c>
+      <c r="I33" s="31">
+        <f>SUM(H33)+0.7</f>
+        <v>7.2</v>
+      </c>
+      <c r="J33" s="31">
+        <f>SUM(I33)+0.7</f>
+        <v>7.9</v>
+      </c>
+      <c r="K33" s="32"/>
+      <c r="L33" s="32"/>
+      <c r="M33" s="143"/>
+    </row>
+    <row r="34" spans="1:13" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="56"/>
+      <c r="B34" s="69" t="s">
+        <v>171</v>
+      </c>
+      <c r="C34" s="70"/>
+      <c r="D34" s="71" t="s">
+        <v>309</v>
+      </c>
+      <c r="E34" s="72"/>
+      <c r="F34" s="72"/>
+      <c r="G34" s="73"/>
+      <c r="H34" s="60"/>
+      <c r="I34" s="61"/>
+      <c r="J34" s="61"/>
+      <c r="K34" s="66"/>
+      <c r="L34" s="66"/>
+      <c r="M34" s="145"/>
+    </row>
+    <row r="35" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="40" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="41" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="42" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="43" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="49" spans="2:7" ht="14.1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="50" spans="2:7" ht="14.1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="51" spans="2:7" ht="14.1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="2:7" ht="14.1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="53" spans="2:7" ht="14.1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="54" spans="2:7" ht="14.1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="55" spans="2:7" ht="14.1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="2:7" ht="14.1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="57" spans="2:7" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+    </row>
+    <row r="58" spans="2:7" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+    </row>
+    <row r="59" spans="2:7" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="179">
+    <mergeCell ref="K33:K34"/>
+    <mergeCell ref="L33:L34"/>
+    <mergeCell ref="M33:M34"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="K31:K32"/>
+    <mergeCell ref="L31:L32"/>
+    <mergeCell ref="M31:M32"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="L29:L30"/>
+    <mergeCell ref="M29:M30"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="K27:K28"/>
+    <mergeCell ref="L27:L28"/>
+    <mergeCell ref="M27:M28"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="L25:L26"/>
+    <mergeCell ref="M25:M26"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="M23:M24"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="K21:K22"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="M21:M22"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="M19:M20"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="K17:K18"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="M17:M18"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="M15:M16"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:G12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+  </mergeCells>
+  <phoneticPr fontId="15" type="noConversion"/>
+  <pageMargins left="0.46875" right="0.46875" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="99" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E52352BA-3245-40C9-93BA-D8EECCB90DF6}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -12375,7 +13556,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -12950,7 +14131,7 @@
         <v>12</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C25" s="44"/>
       <c r="D25" s="53"/>
@@ -12975,7 +14156,7 @@
     <row r="26" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="22"/>
       <c r="B26" s="37" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C26" s="37"/>
       <c r="D26" s="38"/>
@@ -13026,7 +14207,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="129" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C29" s="130"/>
       <c r="D29" s="131"/>
@@ -13051,7 +14232,7 @@
     <row r="30" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="22"/>
       <c r="B30" s="50" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C30" s="51"/>
       <c r="D30" s="38" t="s">
@@ -13072,7 +14253,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C31" s="24"/>
       <c r="D31" s="57"/>
@@ -13097,7 +14278,7 @@
     <row r="32" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="22"/>
       <c r="B32" s="50" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C32" s="51"/>
       <c r="D32" s="38" t="s">
@@ -13118,7 +14299,7 @@
         <v>16</v>
       </c>
       <c r="B33" s="43" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C33" s="44"/>
       <c r="D33" s="53"/>
@@ -13143,11 +14324,11 @@
     <row r="34" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="22"/>
       <c r="B34" s="50" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C34" s="51"/>
       <c r="D34" s="38" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E34" s="39"/>
       <c r="F34" s="39"/>
@@ -13164,7 +14345,7 @@
         <v>17</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C35" s="24"/>
       <c r="D35" s="124" t="s">
@@ -13191,7 +14372,7 @@
     <row r="36" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="22"/>
       <c r="B36" s="23" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C36" s="24"/>
       <c r="D36" s="38" t="s">
@@ -13551,7 +14732,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D2FB2E9-6DC0-4394-837A-E45B184A4CF3}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -13568,7 +14749,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -13663,7 +14844,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C5" s="44"/>
       <c r="D5" s="53"/>
@@ -13688,11 +14869,11 @@
     <row r="6" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="55"/>
       <c r="B6" s="50" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C6" s="51"/>
       <c r="D6" s="38" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E6" s="39"/>
       <c r="F6" s="39"/>
@@ -13928,7 +15109,7 @@
     <row r="16" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="55"/>
       <c r="B16" s="37" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="38" t="s">
@@ -14024,7 +15205,7 @@
     <row r="20" spans="1:16" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="55"/>
       <c r="B20" s="37" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="38" t="s">
@@ -14117,7 +15298,7 @@
       <c r="L23" s="31"/>
       <c r="M23" s="41"/>
       <c r="P23" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="24" spans="1:16" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
@@ -14200,7 +15381,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C27" s="44"/>
       <c r="D27" s="62"/>
@@ -14225,7 +15406,7 @@
     <row r="28" spans="1:16" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="55"/>
       <c r="B28" s="23" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C28" s="24"/>
       <c r="D28" s="25"/>
@@ -14273,7 +15454,7 @@
       </c>
       <c r="C30" s="24"/>
       <c r="D30" s="25" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E30" s="26"/>
       <c r="F30" s="26"/>
@@ -14319,7 +15500,7 @@
       </c>
       <c r="C32" s="51"/>
       <c r="D32" s="38" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E32" s="39"/>
       <c r="F32" s="39"/>
@@ -14650,7 +15831,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -14841,7 +16022,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="52" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C9" s="52"/>
       <c r="D9" s="53"/>
@@ -14866,11 +16047,11 @@
     <row r="10" spans="1:13" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="22"/>
       <c r="B10" s="37" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C10" s="37"/>
       <c r="D10" s="38" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E10" s="39"/>
       <c r="F10" s="39"/>
@@ -15062,7 +16243,7 @@
       </c>
       <c r="C18" s="37"/>
       <c r="D18" s="38" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E18" s="39"/>
       <c r="F18" s="39"/>
@@ -15175,7 +16356,7 @@
         <v>11</v>
       </c>
       <c r="B23" s="43" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C23" s="44"/>
       <c r="D23" s="53"/>
@@ -15200,11 +16381,11 @@
     <row r="24" spans="1:13" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="22"/>
       <c r="B24" s="37" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C24" s="37"/>
       <c r="D24" s="38" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E24" s="39"/>
       <c r="F24" s="39"/>
@@ -15221,7 +16402,7 @@
         <v>12</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C25" s="44"/>
       <c r="D25" s="53"/>
@@ -15246,7 +16427,7 @@
     <row r="26" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="22"/>
       <c r="B26" s="50" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C26" s="51"/>
       <c r="D26" s="38"/>
@@ -15361,7 +16542,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="52" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C31" s="52"/>
       <c r="D31" s="45"/>
@@ -15386,11 +16567,11 @@
     <row r="32" spans="1:13" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="22"/>
       <c r="B32" s="37" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C32" s="37"/>
       <c r="D32" s="38" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E32" s="39"/>
       <c r="F32" s="39"/>
@@ -15436,7 +16617,7 @@
       </c>
       <c r="C34" s="51"/>
       <c r="D34" s="38" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E34" s="39"/>
       <c r="F34" s="39"/>
@@ -15482,7 +16663,7 @@
       </c>
       <c r="C36" s="51"/>
       <c r="D36" s="38" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E36" s="39"/>
       <c r="F36" s="39"/>
@@ -15999,7 +17180,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -16125,7 +17306,7 @@
       </c>
       <c r="C6" s="51"/>
       <c r="D6" s="38" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E6" s="39"/>
       <c r="F6" s="39"/>
@@ -16313,7 +17494,7 @@
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="38" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E14" s="39"/>
       <c r="F14" s="39"/>
@@ -16522,7 +17703,7 @@
         <v>11</v>
       </c>
       <c r="B23" s="52" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C23" s="52"/>
       <c r="D23" s="45"/>
@@ -16547,11 +17728,11 @@
     <row r="24" spans="1:13" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="55"/>
       <c r="B24" s="37" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C24" s="37"/>
       <c r="D24" s="38" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E24" s="39"/>
       <c r="F24" s="39"/>
@@ -16688,7 +17869,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="78" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C31" s="78"/>
       <c r="D31" s="25"/>
@@ -16713,7 +17894,7 @@
     <row r="32" spans="1:13" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="55"/>
       <c r="B32" s="37" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C32" s="37"/>
       <c r="D32" s="38"/>
@@ -17303,7 +18484,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -17878,7 +19059,7 @@
         <v>12</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C25" s="44"/>
       <c r="D25" s="25"/>
@@ -17903,11 +19084,11 @@
     <row r="26" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="22"/>
       <c r="B26" s="50" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C26" s="51"/>
       <c r="D26" s="83" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E26" s="84"/>
       <c r="F26" s="84"/>
@@ -17924,7 +19105,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="52" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C27" s="52"/>
       <c r="D27" s="53"/>
@@ -17949,11 +19130,11 @@
     <row r="28" spans="1:13" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="22"/>
       <c r="B28" s="37" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C28" s="37"/>
       <c r="D28" s="38" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E28" s="39"/>
       <c r="F28" s="39"/>
@@ -18045,7 +19226,7 @@
       </c>
       <c r="C32" s="51"/>
       <c r="D32" s="38" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E32" s="39"/>
       <c r="F32" s="39"/>
@@ -18554,7 +19735,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -18745,7 +19926,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="52" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C9" s="52"/>
       <c r="D9" s="53" t="s">
@@ -18772,11 +19953,11 @@
     <row r="10" spans="1:18" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="55"/>
       <c r="B10" s="37" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C10" s="37"/>
       <c r="D10" s="38" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E10" s="39"/>
       <c r="F10" s="39"/>
@@ -18865,7 +20046,7 @@
       <c r="L13" s="31"/>
       <c r="M13" s="41"/>
       <c r="R13" s="6" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:18" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -18972,7 +20153,7 @@
       <c r="L17" s="31"/>
       <c r="M17" s="41"/>
       <c r="R17" s="6" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:18" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -19151,7 +20332,7 @@
         <v>12</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C25" s="44"/>
       <c r="D25" s="53"/>
@@ -19176,7 +20357,7 @@
     <row r="26" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="55"/>
       <c r="B26" s="50" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C26" s="51"/>
       <c r="D26" s="38"/>
@@ -19239,7 +20420,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="43" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C29" s="44"/>
       <c r="D29" s="53"/>
@@ -19264,7 +20445,7 @@
     <row r="30" spans="1:18" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="55"/>
       <c r="B30" s="50" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C30" s="51"/>
       <c r="D30" s="38"/>
@@ -19283,11 +20464,11 @@
         <v>15</v>
       </c>
       <c r="B31" s="43" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C31" s="44"/>
       <c r="D31" s="46" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E31" s="46"/>
       <c r="F31" s="46"/>
@@ -19310,11 +20491,11 @@
     <row r="32" spans="1:18" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="55"/>
       <c r="B32" s="37" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C32" s="37"/>
       <c r="D32" s="38" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E32" s="39"/>
       <c r="F32" s="39"/>
@@ -19377,7 +20558,7 @@
         <v>17</v>
       </c>
       <c r="B35" s="43" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C35" s="44"/>
       <c r="D35" s="53"/>
@@ -19402,11 +20583,11 @@
     <row r="36" spans="1:13" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="55"/>
       <c r="B36" s="50" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C36" s="51"/>
       <c r="D36" s="88" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E36" s="39"/>
       <c r="F36" s="39"/>
@@ -19423,7 +20604,7 @@
         <v>18</v>
       </c>
       <c r="B37" s="43" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C37" s="44"/>
       <c r="D37" s="53"/>
@@ -19448,11 +20629,11 @@
     <row r="38" spans="1:13" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="55"/>
       <c r="B38" s="50" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C38" s="51"/>
       <c r="D38" s="88" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E38" s="39"/>
       <c r="F38" s="39"/>
@@ -19469,7 +20650,7 @@
         <v>19</v>
       </c>
       <c r="B39" s="43" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C39" s="44"/>
       <c r="D39" s="53"/>
@@ -19494,11 +20675,11 @@
     <row r="40" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="55"/>
       <c r="B40" s="50" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C40" s="51"/>
       <c r="D40" s="88" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E40" s="39"/>
       <c r="F40" s="39"/>
@@ -19544,7 +20725,7 @@
       </c>
       <c r="C42" s="24"/>
       <c r="D42" s="25" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E42" s="26"/>
       <c r="F42" s="26"/>
@@ -19889,7 +21070,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -20412,7 +21593,7 @@
         <v>11</v>
       </c>
       <c r="B23" s="52" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C23" s="52"/>
       <c r="D23" s="45"/>
@@ -20437,11 +21618,11 @@
     <row r="24" spans="1:13" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="55"/>
       <c r="B24" s="37" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C24" s="37"/>
       <c r="D24" s="38" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E24" s="39"/>
       <c r="F24" s="39"/>
@@ -20458,7 +21639,7 @@
         <v>12</v>
       </c>
       <c r="B25" s="78" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C25" s="78"/>
       <c r="D25" s="25"/>
@@ -20483,7 +21664,7 @@
     <row r="26" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="55"/>
       <c r="B26" s="37" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C26" s="37"/>
       <c r="D26" s="38"/>
@@ -21187,7 +22368,6 @@
     <mergeCell ref="D13:G13"/>
     <mergeCell ref="H13:H14"/>
     <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J11:J12"/>
     <mergeCell ref="K11:K12"/>
     <mergeCell ref="L11:L12"/>
     <mergeCell ref="M11:M12"/>
@@ -21199,6 +22379,12 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="D10:G10"/>
     <mergeCell ref="J9:J10"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D6:G6"/>
     <mergeCell ref="A11:A12"/>
@@ -21216,16 +22402,7 @@
     <mergeCell ref="D7:G7"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="I7:I8"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:G5"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J11:J12"/>
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="K7:K8"/>
     <mergeCell ref="L7:L8"/>
@@ -21245,6 +22422,10 @@
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:G4"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -21270,7 +22451,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -21521,7 +22702,7 @@
       </c>
       <c r="C13" s="44"/>
       <c r="D13" s="45" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E13" s="46"/>
       <c r="F13" s="46"/>
@@ -22079,7 +23260,7 @@
         <v>18</v>
       </c>
       <c r="B37" s="43" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C37" s="44"/>
       <c r="D37" s="45"/>
@@ -22104,7 +23285,7 @@
     <row r="38" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="91"/>
       <c r="B38" s="97" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C38" s="98"/>
       <c r="D38" s="83"/>
@@ -22240,7 +23421,7 @@
       </c>
       <c r="C44" s="24"/>
       <c r="D44" s="25" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E44" s="26"/>
       <c r="F44" s="26"/>
@@ -22286,7 +23467,7 @@
       </c>
       <c r="C46" s="51"/>
       <c r="D46" s="25" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E46" s="26"/>
       <c r="F46" s="26"/>
@@ -22616,7 +23797,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -22867,7 +24048,7 @@
       </c>
       <c r="C13" s="44"/>
       <c r="D13" s="45" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E13" s="46"/>
       <c r="F13" s="46"/>
@@ -23113,7 +24294,7 @@
       <c r="L23" s="65"/>
       <c r="M23" s="67"/>
       <c r="P23" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" spans="1:16" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
@@ -23436,7 +24617,7 @@
         <v>18</v>
       </c>
       <c r="B37" s="43" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C37" s="44"/>
       <c r="D37" s="45"/>
@@ -23461,7 +24642,7 @@
     <row r="38" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="91"/>
       <c r="B38" s="97" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C38" s="98"/>
       <c r="D38" s="83"/>
@@ -23597,7 +24778,7 @@
       </c>
       <c r="C44" s="24"/>
       <c r="D44" s="25" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E44" s="26"/>
       <c r="F44" s="26"/>
@@ -23959,7 +25140,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -24981,7 +26162,7 @@
       </c>
       <c r="C46" s="70"/>
       <c r="D46" s="71" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E46" s="72"/>
       <c r="F46" s="72"/>
